--- a/benchmark/generated_files/CRED-1_M_010.xlsx
+++ b/benchmark/generated_files/CRED-1_M_010.xlsx
@@ -433,42 +433,28 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Saldo iniziale: 5.737,51 EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Tipo conto: Carta di credito</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Numero carta: **** **** **** 1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Intestatario: Marco Rossi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Intestatario: Marco Rossi</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Tipo conto: Carta di credito</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Divisa: EUR</t>
+          <t>Periodo: 01/01/2026 - 28/02/2026</t>
         </is>
       </c>
     </row>
@@ -501,18 +487,18 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>46024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELEPASS S.P.A. PEDAGGI</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39.65</v>
+        <v>75.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -522,18 +508,18 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,86 EUR DEL 03.01.2026 A (ITA) PIZZERIA NAPOLI</t>
+          <t>Pagam. POS - PAGAMENTO POS 135,04 EUR DEL 04.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>57.86</v>
+        <v>135.04</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -546,15 +532,15 @@
         <v>46026</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 55,90 EUR DEL 04.01.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8209 BUFFETTI FLAMINIO</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55.9</v>
+        <v>102.03</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -564,18 +550,18 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46030</v>
+        <v>46027</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46032</v>
+        <v>46027</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 61,83 EUR DEL 05.01.2026 A (ITA) CALZEDONIA GROUP</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>79.62</v>
+        <v>61.83</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -585,18 +571,18 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46031</v>
+        <v>46028</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 69,80 EUR DEL 09.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2477 TRATTORIA LA PERGOLA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>69.8</v>
+        <v>19.77</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -606,18 +592,18 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>46032</v>
+        <v>46028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,15 EUR DEL 10.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>96.15000000000001</v>
+        <v>24.72</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -627,18 +613,18 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>46033</v>
+        <v>46029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 71,08 EUR DEL 10.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71.08</v>
+        <v>198.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -648,18 +634,18 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>46032</v>
+        <v>46029</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 135,92 EUR DEL 10.01.2026 A (ITA) LIDL ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 38,76 EUR DEL 07.01.2026 A (ITA) POMPE BIANCHE</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>135.92</v>
+        <v>38.76</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -669,18 +655,18 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>46032</v>
+        <v>46030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 304,59 EUR DEL 10.01.2026 A (ITA) RYANAIR LTD</t>
+          <t>Pagam. POS - PAGAMENTO POS 79,62 EUR DEL 08.01.2026 A (ITA) COOP LOMBARDIA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>304.59</v>
+        <v>79.62</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -690,18 +676,18 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46034</v>
+        <v>46032</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>46034</v>
+        <v>46033</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 53,75 EUR DEL 10.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>71.38</v>
+        <v>53.75</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -711,18 +697,18 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46035</v>
+        <v>46033</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46037</v>
+        <v>46033</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-218767063</t>
+          <t>Pagam. POS - PAGAMENTO POS 115,37 EUR DEL 11.01.2026 A (ITA) MERCATÒ BIG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>298.67</v>
+        <v>115.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -732,18 +718,18 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>46036</v>
+        <v>46035</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-212996787</t>
+          <t>Pagam. POS - PAGAMENTO POS 19,17 EUR DEL 13.01.2026 A (ITA) TACO BELL OSTIENSE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>100.3</v>
+        <v>19.17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -756,15 +742,15 @@
         <v>46036</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 45,87 EUR DEL 14.01.2026 A (ITA) TRENITALIA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4054 ART'OTEL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>45.87</v>
+        <v>151.36</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -774,18 +760,18 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46038</v>
+        <v>46036</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>46039</v>
+        <v>46036</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Pagam. POS - PAGAMENTO POS 134,74 EUR DEL 14.01.2026 A (ITA) INMOTION</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>40.51</v>
+        <v>134.74</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -795,18 +781,18 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>46039</v>
+        <v>46036</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>46039</v>
+        <v>46038</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7571 PITTAROSSO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>308.02</v>
+        <v>148.94</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -816,18 +802,18 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46040</v>
+        <v>46038</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>46040</v>
+        <v>46039</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 53,93 EUR DEL 18.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>53.93</v>
+        <v>40.51</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -837,18 +823,18 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46043</v>
+        <v>46039</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>46044</v>
+        <v>46041</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,71 EUR DEL 21.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6489 TACO BELL</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>32.71</v>
+        <v>64.37</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -858,18 +844,18 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46043</v>
+        <v>46040</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>46045</v>
+        <v>46040</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 41,12 EUR DEL 21.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 53,93 EUR DEL 18.01.2026 A (ITA) SUPERCONTI MODENA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.12</v>
+        <v>53.93</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -879,18 +865,18 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46044</v>
+        <v>46043</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5510 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7956 MALVÓN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>143.43</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -907,11 +893,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>Pagam. POS - PAGAMENTO POS 71,16 EUR DEL 23.01.2026 A (ITA) GIAP</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>178.48</v>
+        <v>71.16</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -921,18 +907,18 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>46046</v>
+        <v>46045</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,91 EUR DEL 24.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6853 COMET</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.91</v>
+        <v>178.48</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -945,15 +931,15 @@
         <v>46046</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>46047</v>
+        <v>46046</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9306 POKE HOUSE MODENA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>234.14</v>
+        <v>53.08</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -970,7 +956,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 146,85 EUR DEL 26.01.2026 A (ITA) HOTEL BELLAVISTA RIMINI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8063 BULGARI BARI</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -987,15 +973,15 @@
         <v>46049</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2319 SPAZIO CONAD CENTRO</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>22.05</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1005,18 +991,18 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>46052</v>
+        <v>46049</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 60,12 EUR DEL 30.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 474,38 EUR DEL 27.01.2026 A (ITA) EXE HOTELS NORD</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>60.12</v>
+        <v>474.38</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1029,15 +1015,15 @@
         <v>46052</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3571 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 48,74 EUR DEL 30.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>53.65</v>
+        <v>48.74</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1047,18 +1033,18 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46053</v>
+        <v>46052</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>46054</v>
+        <v>46052</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 57,86 EUR DEL 31.01.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Pagam. POS - PAGAMENTO POS 60,12 EUR DEL 30.01.2026 A (ITA) THE COFFEE</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>57.86</v>
+        <v>60.12</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1068,18 +1054,18 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46055</v>
+        <v>46054</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 70,03 EUR DEL 02.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3023 OCCIDENTAL LINGOTTO</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>70.03</v>
+        <v>495.15</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1089,18 +1075,18 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 427,90 EUR DEL 04.02.2026 A (ITA) RISTORANTE IL FARO CESENATICO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7921 INMOTION</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>427.9</v>
+        <v>165.92</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1110,18 +1096,18 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>46061</v>
+        <v>46057</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 54,05 EUR DEL 06.02.2026 A (ITA) DISTRIBUTORE ENI</t>
+          <t>Addebito SDD - TELEPASS PEDAGGI A14 AUTOSTRADA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>54.05</v>
+        <v>214.32</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1131,18 +1117,18 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>46061</v>
+        <v>46059</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9574 LIDL ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 16,70 EUR DEL 05.02.2026 A (ITA) SNIPES</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>154.65</v>
+        <v>16.7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1152,18 +1138,18 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>46063</v>
+        <v>46060</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 87,70 EUR DEL 08.02.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>Pagam. POS - PAGAMENTO POS 142,74 EUR DEL 07.02.2026 A (ITA) TRONY</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>87.7</v>
+        <v>142.74</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1180,11 +1166,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 52,65 EUR DEL 08.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 76,57 EUR DEL 08.02.2026 A (ITA) IN'S MERCATO VIMODRONE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>52.65</v>
+        <v>76.56999999999999</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1201,11 +1187,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210383084</t>
+          <t>Pagam. POS - PAGAMENTO POS 371,99 EUR DEL 09.02.2026 A (ITA) ART'OTEL TORINO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>211.28</v>
+        <v>371.99</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1215,18 +1201,18 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46064</v>
+        <v>46062</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 19,39 EUR DEL 11.02.2026 A (ITA) BAR CENTRALE</t>
+          <t>Pagam. POS - PAGAMENTO POS 129,38 EUR DEL 09.02.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>19.39</v>
+        <v>129.38</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1236,18 +1222,18 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B44" s="2" t="n">
         <v>46065</v>
       </c>
-      <c r="B44" s="2" t="n">
-        <v>46066</v>
-      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3969 TRATTORIA LA PERGOLA</t>
+          <t>Pagam. POS - PAGAMENTO POS 46,84 EUR DEL 11.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>8.66</v>
+        <v>46.84</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1257,18 +1243,18 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 164,05 EUR DEL 13.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>Pagam. POS - PAGAMENTO POS 32,19 EUR DEL 12.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>164.05</v>
+        <v>32.19</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1281,15 +1267,15 @@
         <v>46066</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,44 EUR DEL 13.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2743 SPIZZICO ROZZANO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>96.44</v>
+        <v>70.7</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1299,18 +1285,18 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46069</v>
+        <v>46066</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>46070</v>
+        <v>46066</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-218600542</t>
+          <t>Pagam. POS - PAGAMENTO POS 96,44 EUR DEL 13.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>262.37</v>
+        <v>96.44</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1320,18 +1306,18 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 130,47 EUR DEL 16.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1881 BUFFETTI ASSAGO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>130.47</v>
+        <v>284</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1341,18 +1327,18 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B49" s="2" t="n">
         <v>46069</v>
       </c>
-      <c r="B49" s="2" t="n">
-        <v>46070</v>
-      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 82,00 EUR DEL 16.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8971 INMOTION MARGHERA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>82</v>
+        <v>84.61</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1365,15 +1351,15 @@
         <v>46069</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>46069</v>
+        <v>46071</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Addebito SDD - REGISTER.IT S.P.A. DOMINIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 82,00 EUR DEL 16.02.2026 A (ITA) DOPPIO MALTO</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>235.25</v>
+        <v>82</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1383,18 +1369,18 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 400,96 EUR DEL 16.02.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>AMAZON.IT MARKETPLACE - ORDINE 402-211953294</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>400.96</v>
+        <v>117.61</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1404,18 +1390,18 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>46072</v>
+        <v>46071</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 44,40 EUR DEL 18.02.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>117.61</v>
+        <v>44.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1425,18 +1411,18 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>46070</v>
+        <v>46073</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Addebito SDD - GITHUB INC. PRO PLAN</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5510 IES EUR</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>76.70999999999999</v>
+        <v>45.6</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1446,18 +1432,18 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 18,16 EUR DEL 18.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 51,36 EUR DEL 19.02.2026 A (ITA) SPORTLER FLAMINIO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>18.16</v>
+        <v>51.36</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1467,18 +1453,18 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>46077</v>
+        <v>46072</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 403,05 EUR DEL 24.02.2026 A (ITA) BAGNO MARINO N.42 RICCIONE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4283 POKE HOUSE MILANO</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>403.05</v>
+        <v>16.32</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1488,18 +1474,18 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46079</v>
+        <v>46073</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 144,56 EUR DEL 20.02.2026 A (ITA) RYANAIR LTD</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>52.95</v>
+        <v>144.56</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1509,18 +1495,18 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46079</v>
+        <v>46074</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>46080</v>
+        <v>46074</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 73,02 EUR DEL 26.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5406 O'TACOS</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>73.02</v>
+        <v>59.56</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1530,18 +1516,18 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46080</v>
+        <v>46075</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>46080</v>
+        <v>46076</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 46,99 EUR DEL 27.02.2026 A (ITA) ITALO NTV S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3262 POKE HOUSE</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>46.99</v>
+        <v>5.13</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1551,18 +1537,18 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46080</v>
+        <v>46076</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>46080</v>
+        <v>46078</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Pagam. POS - PAGAMENTO POS 146,94 EUR DEL 23.02.2026 A (ITA) CEX</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>164.35</v>
+        <v>146.94</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1572,18 +1558,18 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>46082</v>
+        <v>46078</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 89,24 EUR DEL 28.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4065 MIGROSS OVEST</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>89.23999999999999</v>
+        <v>162.98</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1593,18 +1579,18 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46081</v>
+        <v>46078</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>46081</v>
+        <v>46079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Addebito SDD - SARA ASSICURAZIONI RCA AUTO</t>
+          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>34.64</v>
+        <v>41.6</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
